--- a/assessment_forms/002_jet_lag_sleep_assessment--assessment_forms.xlsx
+++ b/assessment_forms/002_jet_lag_sleep_assessment--assessment_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,9 +431,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>day_1</t>
+          <t>day_1_hours</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 1 Hours</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>day_2</t>
+          <t>day_2_hours</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 2 Hours</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>day_3</t>
+          <t>day_3_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 3 Hours</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>day_4</t>
+          <t>day_4_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 4 Hours</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>day_5</t>
+          <t>day_5_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 5 Hours</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>day_6</t>
+          <t>day_6_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 6 Hours</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>day_7</t>
+          <t>day_7_hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 7 Hours</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,19 +671,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>day_8</t>
+          <t>day_8_hours</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
+          <t>Day 8 Hours</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -698,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>day_9</t>
+          <t>day_9_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 9 Hours</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -721,18 +717,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>day_10</t>
+          <t>day_10_hours</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 10 Hours</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -744,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>day_11</t>
+          <t>day_11_hours</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 11 Hours</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -767,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>day_12</t>
+          <t>day_12_hours</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 12 Hours</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -790,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>day_13</t>
+          <t>day_13_hours</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 13 Hours</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -813,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>day_14</t>
+          <t>day_14_hours</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 14 Hours</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -836,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>day_15</t>
+          <t>day_15_hours</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 15 Hours</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -859,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>day_16</t>
+          <t>day_16_hours</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 16 Hours</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -882,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>day_17</t>
+          <t>day_17_hours</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 17 Hours</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -905,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>day_18</t>
+          <t>day_18_hours</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 18 Hours</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -928,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>day_19</t>
+          <t>day_19_hours</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 19 Hours</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -951,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>day_20</t>
+          <t>day_20_hours</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 20 Hours</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -974,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>day_21</t>
+          <t>day_21_hours</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 21 Hours</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -997,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>day_22</t>
+          <t>day_22_hours</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 22 Hours</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1020,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>day_23</t>
+          <t>day_23_hours</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 23 Hours</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1043,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>day_24</t>
+          <t>day_24_hours</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 24 Hours</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1066,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>day_25</t>
+          <t>day_25_hours</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morning Wake Up Time</t>
+          <t>Day 25 Hours</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
